--- a/research/06_scope_redesign/p1_meet_20261020/DATA_INVENTORY_BRIEF.xlsx
+++ b/research/06_scope_redesign/p1_meet_20261020/DATA_INVENTORY_BRIEF.xlsx
@@ -464,7 +464,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>注册表 2,052 行（880955b8，SHA256 6950a15d…8dd2）；全部数字为脚本实算；详表见 DATA_INVENTORY_v2.xlsx。</t>
+          <t>注册表 2,057 行（1be5ce02，SHA256 6d1b2c34…0fa4）；全部数字为脚本实算；详表见 DATA_INVENTORY_v3.xlsx。</t>
         </is>
       </c>
     </row>
@@ -542,11 +542,11 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>12.8 %</t>
+          <t>13.0 %</t>
         </is>
       </c>
     </row>
@@ -557,11 +557,11 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>1301</v>
+        <v>1290</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>63.4 %</t>
+          <t>62.7 %</t>
         </is>
       </c>
     </row>
@@ -572,11 +572,11 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>23.8 %</t>
+          <t>24.3 %</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>2052</v>
+        <v>2057</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>55.7 %</t>
+          <t>55.5 %</t>
         </is>
       </c>
     </row>
@@ -641,11 +641,11 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>26.8 %</t>
+          <t>27.0 %</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>2052</v>
+        <v>2057</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
@@ -789,12 +789,12 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>774（61.28 %）</t>
+          <t>762（60.33 %）</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>352（27.87 %）</t>
+          <t>364（28.82 %）</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>803（62.15 %）</t>
+          <t>791（61.22 %）</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>352（27.24 %）</t>
+          <t>364（28.17 %）</t>
         </is>
       </c>
     </row>
@@ -839,12 +839,12 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>684（61.46 %）</t>
+          <t>672（60.38 %）</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>318（28.57 %）</t>
+          <t>330（29.65 %）</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>年总量取自需求表中居民、商业、农业及其他与 2019 年交通电力；小时形状为 GEGIS（GlobalEnergyGIS）2030 年国别负荷曲线（SSP2-RCP2.6，ERA5 2013 天气年；PyPSA-Earth 数据包），LA、TL 分别借用 KH、ID 曲线</t>
+          <t>年总量取自需求表中居民、商业、农业及其他与 2019 年交通电力；小时形状为 GEGIS（GlobalEnergyGIS；Mattsson et al. 2021, Energy Strategy Reviews 33, 100606）2030 年国别负荷曲线（SSP2-RCP2.6，ERA5 2013 天气年；PyPSA-Earth 数据包）；LA、TL 分别借用 KH、ID 曲线（例外，C 级）</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>2050 产量 = min（2024 基年 × GDP 增长弹性，人均饱和 × 人口，国家规划上限），11 国同一规则；VN 水泥 581 → 107.0 Mt、粗钢 80.3 → 40.7 Mt（已确定方案，尚未实施）</t>
+          <t>2050 产量 = min（基年 × GDP 增长弹性，人均饱和 × 人口，国家规划上限），11 国同一规则；基年水泥 2023（USGS 年鉴）、粗钢 2024（worldsteel）；VN 水泥 581 → 107.0 Mt、粗钢 80.3 → 40.7 Mt（按原基年估算，M08 按新文件重算）（已确定方案，尚未实施）</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>主算行 12：B 12</t>
+          <t>主算行 12：C 12</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>11 国均有候选；建筑原始数据不在本机，未本地复算</t>
+          <t>11 国均有候选；建筑原始数据不在本机，无法复现，定为 C 级（±50 %）</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>改用欧元区 HICP 回算，消除 +4.8 % 残余（已确定方案，尚未实施）</t>
+          <t>按 technology-data 同一通胀口径（欧洲经济区 HICP 年变化率）回算，消除 +4.8 % 残余；存量机组改用 v0.15.0 对应年份（已确定方案，尚未实施）</t>
         </is>
       </c>
     </row>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>存量运维费按年份统一平减到 2020 年（重建时）</t>
+          <t>存量运维费按年份统一平减到 2020 年；存量成本与效率改用 technology-data v0.15.0 对应投运年份（重建时）</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>潜力已登记，成本缺失（过渡值注册表未写明）</t>
+          <t>潜力已登记，成本缺失（注册表未写明替代值）</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>二手引述 1.889 M</t>
+          <t>已获取（unpopulation_dataportal_20261020224306.csv：UN WPP 2024，TL 2050 中位 1,889,249.5 人），M08 实施</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>下载清单 A4（UN WPP 2024）</t>
+          <t>M08 实施</t>
         </is>
       </c>
     </row>
@@ -3404,22 +3404,22 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>USGS 年鉴水泥世界表（2024 基年）</t>
+          <t>USGS 年鉴水泥世界表（水泥基年 2023）</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>TH、MY、PH、KH、LA、MM、BN</t>
+          <t>11 国（SG、TL 不在表中，按 0）</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>国家统计二手值或 EDGAR 2019 值持平（过渡值）</t>
+          <t>已获取（myb1-2023-cemen-ERT.xlsx：USGS 年鉴 2023 水泥表 T22，2019–2023 年），M08 实施；水泥基年 2023，11 国同一来源</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>下载清单 A2</t>
+          <t>M08 实施</t>
         </is>
       </c>
     </row>
@@ -3434,22 +3434,22 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>worldsteel 2024 粗钢</t>
+          <t>worldsteel 粗钢产量（钢铁基年 2024）</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>SG、MM</t>
+          <t>11 国（BN、KH、LA、TL 不在表中，按 0）</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>2019 值持平（SG 0.77、MM 0.35 Mt）</t>
+          <t>已获取（exp-2026-10-20_15_02_22.xlsx：worldsteel Steel Data Viewer，2021–2025 年），M08 实施；钢铁基年 2024，11 国同一来源</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>下载清单 A3（Steel Data Viewer）</t>
+          <t>M08 实施</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Eurostat HICP 年均指数</t>
+          <t>Eurostat HICP 年均指数与年变化率</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>现用 EA20 GDP 平减（残余 +4.8 %）</t>
+          <t>已获取（prc_hicp_aind$defaultview_spreadsheet.xlsx：Eurostat HICP 2016–2025），M08 实施；technology-data v0.15.0 按欧洲经济区（EEA）年均变化率升通胀（2020→2025 系数 1.2573），回算用同一口径</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>下载清单 A5（prc_hicp_aind）</t>
+          <t>M08 实施</t>
         </is>
       </c>
     </row>
